--- a/ExcelFiles/Login_Details.xlsx
+++ b/ExcelFiles/Login_Details.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="4">
   <si>
     <t>Admin</t>
   </si>
@@ -93,10 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -391,7 +394,7 @@
       <c r="B1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C1" t="s" s="6">
+      <c r="C1" t="s" s="9">
         <v>1</v>
       </c>
     </row>
